--- a/Dahbsim_Output_GM.xlsx
+++ b/Dahbsim_Output_GM.xlsx
@@ -496,13 +496,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8506.084106392787</v>
+        <v>8506.084106392889</v>
       </c>
       <c r="E2" t="n">
-        <v>8186.974149171922</v>
+        <v>8186.974149171931</v>
       </c>
       <c r="F2" t="n">
-        <v>7951.672392666108</v>
+        <v>7951.672392666117</v>
       </c>
     </row>
   </sheetData>
@@ -554,7 +554,7 @@
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>96.00000000000006</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14916.36650000001</v>
+        <v>14916.3665</v>
       </c>
       <c r="E2" t="n">
-        <v>7693.066666666691</v>
+        <v>7693.066666666669</v>
       </c>
       <c r="F2" t="n">
-        <v>7693.066666666696</v>
+        <v>7693.066666666669</v>
       </c>
     </row>
   </sheetData>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>88.74388472060515</v>
+        <v>1243.1848664</v>
       </c>
       <c r="E2" t="n">
-        <v>94.7946090814246</v>
+        <v>562.916695488</v>
       </c>
       <c r="F2" t="n">
-        <v>97.27452217859164</v>
+        <v>551.5660906224</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>855.5942824088971</v>
+        <v>855.594282408897</v>
       </c>
       <c r="E2" t="n">
         <v>820.1796147178566</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8506.084106392787</v>
+        <v>8506.084106392889</v>
       </c>
       <c r="E2" t="n">
-        <v>8186.974149171922</v>
+        <v>8186.974149171931</v>
       </c>
       <c r="F2" t="n">
-        <v>7951.672392666108</v>
+        <v>7951.672392666117</v>
       </c>
     </row>
   </sheetData>
@@ -836,10 +836,10 @@
         <v>2154.9575</v>
       </c>
       <c r="E2" t="n">
-        <v>2542.760409219955</v>
+        <v>2542.760409219958</v>
       </c>
       <c r="F2" t="n">
-        <v>2542.760409219957</v>
+        <v>2542.760409219958</v>
       </c>
     </row>
   </sheetData>
@@ -880,13 +880,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88.74388472060515</v>
+        <v>1243.1848664</v>
       </c>
       <c r="C2" t="n">
-        <v>94.7946090814246</v>
+        <v>562.916695488</v>
       </c>
       <c r="D2" t="n">
-        <v>97.27452217859164</v>
+        <v>551.5660906224</v>
       </c>
     </row>
   </sheetData>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8506.084106392787</v>
+        <v>8506.084106392889</v>
       </c>
       <c r="C2" t="n">
-        <v>8186.974149171922</v>
+        <v>8186.974149171931</v>
       </c>
       <c r="D2" t="n">
-        <v>7951.672392666108</v>
+        <v>7951.672392666117</v>
       </c>
     </row>
   </sheetData>
@@ -1024,10 +1024,10 @@
         <v>0.019235</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0187202</v>
+        <v>10.0059202</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01837271</v>
+        <v>10.00557271</v>
       </c>
     </row>
   </sheetData>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1286.141999999839</v>
+        <v>1286.142</v>
       </c>
       <c r="E2" t="n">
         <v/>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>779.2154999998415</v>
+        <v>779.2155</v>
       </c>
       <c r="E3" t="n">
-        <v>2519.080409219956</v>
+        <v>2519.080409219958</v>
       </c>
       <c r="F3" t="n">
         <v>2519.080409219958</v>
@@ -1133,10 +1133,10 @@
         <v>18215.1458775</v>
       </c>
       <c r="E4" t="n">
-        <v>17000.80281899998</v>
+        <v>17000.802819</v>
       </c>
       <c r="F4" t="n">
-        <v>16454.34844267498</v>
+        <v>16454.348442675</v>
       </c>
     </row>
   </sheetData>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7915</v>
+        <v>5.791499999999999</v>
       </c>
       <c r="C2" t="n">
         <v>5.328180000000001</v>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2404.56322666667</v>
+        <v>2404.563226666667</v>
       </c>
       <c r="C2" t="n">
-        <v>1059.373620533352</v>
+        <v>1059.373620533333</v>
       </c>
       <c r="D2" t="n">
-        <v>1047.693168893352</v>
+        <v>1047.693168893333</v>
       </c>
     </row>
   </sheetData>
@@ -1274,10 +1274,10 @@
         <v>0.006399999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006400000000000007</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0064</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>598.8542672665723</v>
+        <v>598.8542672666667</v>
       </c>
       <c r="C2" t="n">
-        <v>769.942932186916</v>
+        <v>769.9429321869178</v>
       </c>
       <c r="D2" t="n">
-        <v>769.9429321869179</v>
+        <v>769.9429321869178</v>
       </c>
     </row>
     <row r="3">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8095.620389999993</v>
+        <v>8095.62039</v>
       </c>
       <c r="C3" t="n">
-        <v>7555.912363999993</v>
+        <v>7555.912363999999</v>
       </c>
       <c r="D3" t="n">
         <v>7313.043752300001</v>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7915</v>
+        <v>5.791499999999999</v>
       </c>
       <c r="C2" t="n">
         <v>5.328180000000001</v>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.086138967262626</v>
+        <v>1032.98847</v>
       </c>
       <c r="C2" t="n">
-        <v>6.880954333029562</v>
+        <v>369.53601</v>
       </c>
       <c r="D2" t="n">
-        <v>6.880954333029561</v>
+        <v>369.53601</v>
       </c>
     </row>
     <row r="3">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86.65774575334252</v>
+        <v>210.1963964</v>
       </c>
       <c r="C3" t="n">
-        <v>87.91365474839503</v>
+        <v>193.380685488</v>
       </c>
       <c r="D3" t="n">
-        <v>90.39356784556207</v>
+        <v>182.0300806224</v>
       </c>
     </row>
   </sheetData>
@@ -1596,7 +1596,7 @@
         <v/>
       </c>
       <c r="G3" t="n">
-        <v>1.936666666666665</v>
+        <v>1.936666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>96.00000000000006</v>
+        <v>96</v>
       </c>
       <c r="E6" t="n">
         <v/>
@@ -1712,7 +1712,7 @@
         <v/>
       </c>
       <c r="G7" t="n">
-        <v>2.133333333333332</v>
+        <v>2.133333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -1735,7 +1735,7 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>57.915</v>
+        <v>57.91499999999999</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -1828,7 +1828,7 @@
         <v/>
       </c>
       <c r="F11" t="n">
-        <v>7.830977439999996</v>
+        <v>7.83097744</v>
       </c>
       <c r="G11" t="n">
         <v/>
@@ -1886,7 +1886,7 @@
         <v/>
       </c>
       <c r="F13" t="n">
-        <v>7.371333112000001</v>
+        <v>7.371333112</v>
       </c>
       <c r="G13" t="n">
         <v/>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1286.141999999839</v>
+        <v>1286.142</v>
       </c>
       <c r="E2" t="n">
         <v/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>779.2154999998415</v>
+        <v>779.2155</v>
       </c>
       <c r="E3" t="n">
-        <v>2519.080409219956</v>
+        <v>2519.080409219958</v>
       </c>
       <c r="F3" t="n">
         <v>2519.080409219958</v>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.694065894508601e-21</v>
+        <v/>
       </c>
       <c r="E4" t="n">
         <v/>
@@ -2370,7 +2370,7 @@
         <v>104.704</v>
       </c>
       <c r="D3" t="n">
-        <v>104.7040000000001</v>
+        <v>104.704</v>
       </c>
     </row>
     <row r="4">
@@ -2383,7 +2383,7 @@
         <v>96.84674999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>89.09901000000002</v>
+        <v>89.09900999999998</v>
       </c>
       <c r="D4" t="n">
         <v>83.8692855</v>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>545.7803567110167</v>
+        <v>545.7803567111113</v>
       </c>
       <c r="D2" t="n">
-        <v>755.6798921869159</v>
+        <v>755.6798921869178</v>
       </c>
       <c r="E2" t="n">
-        <v>755.6798921869167</v>
+        <v>755.6798921869178</v>
       </c>
     </row>
     <row r="3">
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7958.081527459548</v>
+        <v>7958.081527459555</v>
       </c>
       <c r="D3" t="n">
-        <v>7429.072034762784</v>
+        <v>7429.07203476279</v>
       </c>
       <c r="E3" t="n">
         <v>7193.770278256977</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2354.54931666667</v>
+        <v>2354.549316666667</v>
       </c>
       <c r="D4" t="n">
-        <v>1054.176343333351</v>
+        <v>1054.176343333333</v>
       </c>
       <c r="E4" t="n">
-        <v>1048.946618833352</v>
+        <v>1048.946618833333</v>
       </c>
     </row>
     <row r="5">
@@ -2519,10 +2519,10 @@
         <v>0.006399999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006400000000000007</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0064</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2537,13 +2537,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>88.74388472060515</v>
+        <v>1243.1848664</v>
       </c>
       <c r="D7" t="n">
-        <v>94.7946090814246</v>
+        <v>562.916695488</v>
       </c>
       <c r="E7" t="n">
-        <v>97.27452217859164</v>
+        <v>551.5660906224</v>
       </c>
     </row>
   </sheetData>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.818989403545856e-11</v>
+        <v>1.455191522836685e-11</v>
       </c>
     </row>
     <row r="4">
@@ -2778,13 +2778,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.87996497777781</v>
+        <v>52.87996497777777</v>
       </c>
       <c r="C2" t="n">
-        <v>14.19377777777782</v>
+        <v>14.19377777777778</v>
       </c>
       <c r="D2" t="n">
-        <v>14.19377777777782</v>
+        <v>14.19377777777778</v>
       </c>
     </row>
     <row r="3">
@@ -2794,13 +2794,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1939455777777779</v>
+        <v>0.1939455777777778</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06926222222222225</v>
+        <v>0.06926222222222223</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06926222222222229</v>
+        <v>0.06926222222222223</v>
       </c>
     </row>
     <row r="4">
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137.5112309999999</v>
+        <v>137.511231</v>
       </c>
       <c r="C4" t="n">
-        <v>126.8149082199999</v>
+        <v>126.81490822</v>
       </c>
       <c r="D4" t="n">
         <v>119.249545129</v>
@@ -2829,10 +2829,10 @@
         <v>0.02763154044444444</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02542101720889178</v>
+        <v>0.02542101720888889</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02392891402489293</v>
+        <v>0.02392891402488889</v>
       </c>
     </row>
   </sheetData>
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>598.8542672665723</v>
+        <v>598.8542672666667</v>
       </c>
       <c r="C2" t="n">
-        <v>769.942932186916</v>
+        <v>769.9429321869178</v>
       </c>
       <c r="D2" t="n">
-        <v>769.9429321869179</v>
+        <v>769.9429321869178</v>
       </c>
     </row>
     <row r="3">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8095.620389999993</v>
+        <v>8095.62039</v>
       </c>
       <c r="C3" t="n">
-        <v>7555.912363999993</v>
+        <v>7555.912363999999</v>
       </c>
       <c r="D3" t="n">
         <v>7313.043752300001</v>
@@ -61010,10 +61010,10 @@
         <v>779.2155</v>
       </c>
       <c r="E3" t="n">
-        <v>2542.760409219955</v>
+        <v>2542.760409219958</v>
       </c>
       <c r="F3" t="n">
-        <v>2542.760409219957</v>
+        <v>2542.760409219958</v>
       </c>
     </row>
   </sheetData>
@@ -61059,13 +61059,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17052.85822467654</v>
+        <v>17052.85822467665</v>
       </c>
       <c r="D2" t="n">
-        <v>16076.88371918444</v>
+        <v>16076.88371918447</v>
       </c>
       <c r="E2" t="n">
-        <v>15615.99180534325</v>
+        <v>15615.99180534326</v>
       </c>
     </row>
   </sheetData>
@@ -61189,14 +61189,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>maize_c</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>wheat_c</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>imp_maize</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>field1</t>
@@ -61213,13 +61213,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v/>
+        <v>0.21</v>
       </c>
       <c r="H4" t="n">
         <v/>
       </c>
       <c r="I4" t="n">
-        <v>1.694065894508601e-21</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -61230,7 +61230,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>maize_c</t>
+          <t>imp_maize</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -61254,10 +61254,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.21</v>
+        <v/>
       </c>
       <c r="H5" t="n">
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="I5" t="n">
         <v/>
@@ -61276,7 +61276,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wheat_c</t>
+          <t>maize_c</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -61298,7 +61298,7 @@
         <v/>
       </c>
       <c r="H6" t="n">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
       <c r="I6" t="n">
         <v/>
@@ -61317,7 +61317,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>maize_c</t>
+          <t>imp_maize</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -61339,10 +61339,10 @@
         <v/>
       </c>
       <c r="H7" t="n">
-        <v>0.21</v>
+        <v/>
       </c>
       <c r="I7" t="n">
-        <v/>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8">
@@ -61375,12 +61375,6 @@
         <is>
           <t>area</t>
         </is>
-      </c>
-      <c r="G8" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
       </c>
       <c r="I8" t="n">
         <v>0.64</v>
@@ -61522,7 +61516,7 @@
         <v>3199.4</v>
       </c>
       <c r="H2" t="n">
-        <v>699.4</v>
+        <v>699.4000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>699.4000000000001</v>
@@ -61563,7 +61557,7 @@
         <v>3057.01</v>
       </c>
       <c r="H3" t="n">
-        <v>557.01</v>
+        <v>557.0100000000002</v>
       </c>
       <c r="I3" t="n">
         <v>557.0100000000002</v>
@@ -61645,7 +61639,7 @@
         <v>3199.4</v>
       </c>
       <c r="H5" t="n">
-        <v>699.4</v>
+        <v>699.4000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>699.4000000000001</v>
@@ -61686,7 +61680,7 @@
         <v>3057.01</v>
       </c>
       <c r="H6" t="n">
-        <v>557.01</v>
+        <v>557.0100000000002</v>
       </c>
       <c r="I6" t="n">
         <v>557.0100000000002</v>
@@ -61768,7 +61762,7 @@
         <v>3199.4</v>
       </c>
       <c r="H8" t="n">
-        <v>699.4</v>
+        <v>699.4000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>699.4000000000001</v>
@@ -61809,7 +61803,7 @@
         <v>3057.01</v>
       </c>
       <c r="H9" t="n">
-        <v>557.01</v>
+        <v>557.0100000000002</v>
       </c>
       <c r="I9" t="n">
         <v>557.0100000000002</v>
@@ -61891,7 +61885,7 @@
         <v>3199.4</v>
       </c>
       <c r="H11" t="n">
-        <v>699.4</v>
+        <v>699.4000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>699.4000000000001</v>
@@ -61932,7 +61926,7 @@
         <v>3057.01</v>
       </c>
       <c r="H12" t="n">
-        <v>557.01</v>
+        <v>557.0100000000002</v>
       </c>
       <c r="I12" t="n">
         <v>557.0100000000002</v>
@@ -62014,7 +62008,7 @@
         <v>3199.4</v>
       </c>
       <c r="H14" t="n">
-        <v>699.4</v>
+        <v>699.4000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>699.4000000000001</v>
@@ -62055,7 +62049,7 @@
         <v>3057.01</v>
       </c>
       <c r="H15" t="n">
-        <v>557.01</v>
+        <v>557.0100000000002</v>
       </c>
       <c r="I15" t="n">
         <v>557.0100000000002</v>
@@ -62137,7 +62131,7 @@
         <v>3710.55</v>
       </c>
       <c r="H17" t="n">
-        <v>3375.265149029</v>
+        <v>3375.265149028999</v>
       </c>
       <c r="I17" t="n">
         <v>3375.265149028999</v>
@@ -62178,7 +62172,7 @@
         <v>3279.44</v>
       </c>
       <c r="H18" t="n">
-        <v>2944.155149029</v>
+        <v>2944.155149028998</v>
       </c>
       <c r="I18" t="n">
         <v>2944.155149028998</v>
@@ -62219,7 +62213,7 @@
         <v>2847.83</v>
       </c>
       <c r="H19" t="n">
-        <v>2544.3960188665</v>
+        <v>2544.396018866495</v>
       </c>
       <c r="I19" t="n">
         <v>2544.396018866495</v>
@@ -62260,7 +62254,7 @@
         <v>3710.55</v>
       </c>
       <c r="H20" t="n">
-        <v>3375.265149029</v>
+        <v>3375.265149028999</v>
       </c>
       <c r="I20" t="n">
         <v>3375.265149028999</v>
@@ -62301,7 +62295,7 @@
         <v>3279.44</v>
       </c>
       <c r="H21" t="n">
-        <v>2944.155149029</v>
+        <v>2944.155149028998</v>
       </c>
       <c r="I21" t="n">
         <v>2944.155149028998</v>
@@ -62342,7 +62336,7 @@
         <v>2847.83</v>
       </c>
       <c r="H22" t="n">
-        <v>2544.3960188665</v>
+        <v>2544.396018866495</v>
       </c>
       <c r="I22" t="n">
         <v>2544.396018866495</v>
@@ -62383,7 +62377,7 @@
         <v>3710.55</v>
       </c>
       <c r="H23" t="n">
-        <v>3375.265149029</v>
+        <v>3375.265149028999</v>
       </c>
       <c r="I23" t="n">
         <v>3375.265149028999</v>
@@ -62424,7 +62418,7 @@
         <v>3279.44</v>
       </c>
       <c r="H24" t="n">
-        <v>2944.155149029</v>
+        <v>2944.155149028998</v>
       </c>
       <c r="I24" t="n">
         <v>2944.155149028998</v>
@@ -62465,7 +62459,7 @@
         <v>2847.83</v>
       </c>
       <c r="H25" t="n">
-        <v>2544.3960188665</v>
+        <v>2544.396018866495</v>
       </c>
       <c r="I25" t="n">
         <v>2544.396018866495</v>
@@ -62506,7 +62500,7 @@
         <v>3710.55</v>
       </c>
       <c r="H26" t="n">
-        <v>3375.265149029</v>
+        <v>3375.265149028999</v>
       </c>
       <c r="I26" t="n">
         <v>3375.265149028999</v>
@@ -62547,7 +62541,7 @@
         <v>3279.44</v>
       </c>
       <c r="H27" t="n">
-        <v>2944.155149029</v>
+        <v>2944.155149028998</v>
       </c>
       <c r="I27" t="n">
         <v>2944.155149028998</v>
@@ -62588,7 +62582,7 @@
         <v>2847.83</v>
       </c>
       <c r="H28" t="n">
-        <v>2544.3960188665</v>
+        <v>2544.396018866495</v>
       </c>
       <c r="I28" t="n">
         <v>2544.396018866495</v>
@@ -62629,7 +62623,7 @@
         <v>3710.55</v>
       </c>
       <c r="H29" t="n">
-        <v>3375.265149029</v>
+        <v>3375.265149028999</v>
       </c>
       <c r="I29" t="n">
         <v>3375.265149028999</v>
@@ -62670,7 +62664,7 @@
         <v>3279.44</v>
       </c>
       <c r="H30" t="n">
-        <v>2944.155149029</v>
+        <v>2944.155149028998</v>
       </c>
       <c r="I30" t="n">
         <v>2944.155149028998</v>
@@ -62711,7 +62705,7 @@
         <v>2847.83</v>
       </c>
       <c r="H31" t="n">
-        <v>2544.3960188665</v>
+        <v>2544.396018866495</v>
       </c>
       <c r="I31" t="n">
         <v>2544.396018866495</v>
@@ -62752,7 +62746,7 @@
         <v/>
       </c>
       <c r="H32" t="n">
-        <v>1224.71481845123</v>
+        <v>1224.714818451228</v>
       </c>
       <c r="I32" t="n">
         <v>458.3036306319736</v>
@@ -62793,7 +62787,7 @@
         <v/>
       </c>
       <c r="H33" t="n">
-        <v>1898.97802052478</v>
+        <v>1898.978020524784</v>
       </c>
       <c r="I33" t="n">
         <v>703.3437812073835</v>
@@ -62834,7 +62828,7 @@
         <v/>
       </c>
       <c r="H34" t="n">
-        <v>1224.71481845123</v>
+        <v>1224.714818451228</v>
       </c>
       <c r="I34" t="n">
         <v>458.3036306319736</v>
@@ -62875,7 +62869,7 @@
         <v/>
       </c>
       <c r="H35" t="n">
-        <v>1898.97802052478</v>
+        <v>1898.978020524784</v>
       </c>
       <c r="I35" t="n">
         <v>703.3437812073835</v>
@@ -62916,7 +62910,7 @@
         <v>4300</v>
       </c>
       <c r="H36" t="n">
-        <v>5524.71481845123</v>
+        <v>5524.714818451228</v>
       </c>
       <c r="I36" t="n">
         <v>4758.303630631974</v>
@@ -62957,7 +62951,7 @@
         <v>4000</v>
       </c>
       <c r="H37" t="n">
-        <v>5898.97802052478</v>
+        <v>5898.978020524784</v>
       </c>
       <c r="I37" t="n">
         <v>4703.343781207383</v>
@@ -62998,7 +62992,7 @@
         <v>3900</v>
       </c>
       <c r="H38" t="n">
-        <v>3682.12628452054</v>
+        <v>3682.126284520538</v>
       </c>
       <c r="I38" t="n">
         <v>3682.126284520538</v>
@@ -63039,7 +63033,7 @@
         <v>4300</v>
       </c>
       <c r="H39" t="n">
-        <v>5524.71481845123</v>
+        <v>5524.714818451228</v>
       </c>
       <c r="I39" t="n">
         <v>4758.303630631974</v>
@@ -63080,7 +63074,7 @@
         <v>4000</v>
       </c>
       <c r="H40" t="n">
-        <v>5898.97802052478</v>
+        <v>5898.978020524784</v>
       </c>
       <c r="I40" t="n">
         <v>4703.343781207383</v>
@@ -63121,7 +63115,7 @@
         <v>3900</v>
       </c>
       <c r="H41" t="n">
-        <v>3682.12628452054</v>
+        <v>3682.126284520538</v>
       </c>
       <c r="I41" t="n">
         <v>3682.126284520538</v>
@@ -63162,7 +63156,7 @@
         <v/>
       </c>
       <c r="H42" t="n">
-        <v>1224.71481845123</v>
+        <v>1224.714818451228</v>
       </c>
       <c r="I42" t="n">
         <v>458.3036306319736</v>
@@ -63203,7 +63197,7 @@
         <v/>
       </c>
       <c r="H43" t="n">
-        <v>1898.97802052478</v>
+        <v>1898.978020524784</v>
       </c>
       <c r="I43" t="n">
         <v>703.3437812073835</v>
@@ -63244,7 +63238,7 @@
         <v/>
       </c>
       <c r="H44" t="n">
-        <v>1224.71481845123</v>
+        <v>1224.714818451228</v>
       </c>
       <c r="I44" t="n">
         <v>458.3036306319736</v>
@@ -63285,7 +63279,7 @@
         <v/>
       </c>
       <c r="H45" t="n">
-        <v>1898.97802052478</v>
+        <v>1898.978020524784</v>
       </c>
       <c r="I45" t="n">
         <v>703.3437812073835</v>
@@ -63326,7 +63320,7 @@
         <v/>
       </c>
       <c r="H46" t="n">
-        <v>1224.71481845123</v>
+        <v>1224.714818451228</v>
       </c>
       <c r="I46" t="n">
         <v>458.3036306319736</v>
@@ -63367,7 +63361,7 @@
         <v/>
       </c>
       <c r="H47" t="n">
-        <v>1898.97802052478</v>
+        <v>1898.978020524784</v>
       </c>
       <c r="I47" t="n">
         <v>703.3437812073835</v>
@@ -63408,7 +63402,7 @@
         <v>2937.48</v>
       </c>
       <c r="H48" t="n">
-        <v>2856.26325404212</v>
+        <v>2856.263254042118</v>
       </c>
       <c r="I48" t="n">
         <v>2856.263254042118</v>
@@ -63449,7 +63443,7 @@
         <v>2239.87</v>
       </c>
       <c r="H49" t="n">
-        <v>1735.38714402385</v>
+        <v>1735.387144023848</v>
       </c>
       <c r="I49" t="n">
         <v>1735.387144023848</v>
@@ -63490,7 +63484,7 @@
         <v>2239.87</v>
       </c>
       <c r="H50" t="n">
-        <v>1735.38714402385</v>
+        <v>1735.387144023848</v>
       </c>
       <c r="I50" t="n">
         <v>1735.387144023848</v>
@@ -63531,7 +63525,7 @@
         <v>2937.48</v>
       </c>
       <c r="H51" t="n">
-        <v>2856.26325404212</v>
+        <v>2856.263254042118</v>
       </c>
       <c r="I51" t="n">
         <v>2856.263254042118</v>
@@ -63572,7 +63566,7 @@
         <v>2239.87</v>
       </c>
       <c r="H52" t="n">
-        <v>1735.38714402385</v>
+        <v>1735.387144023848</v>
       </c>
       <c r="I52" t="n">
         <v>1735.387144023848</v>
@@ -63613,7 +63607,7 @@
         <v>2239.87</v>
       </c>
       <c r="H53" t="n">
-        <v>1735.38714402385</v>
+        <v>1735.387144023848</v>
       </c>
       <c r="I53" t="n">
         <v>1735.387144023848</v>
@@ -63654,7 +63648,7 @@
         <v>5200</v>
       </c>
       <c r="H54" t="n">
-        <v>2721.14804025373</v>
+        <v>2721.148040253726</v>
       </c>
       <c r="I54" t="n">
         <v>2721.148040253726</v>
@@ -63695,7 +63689,7 @@
         <v>5000</v>
       </c>
       <c r="H55" t="n">
-        <v>2521.14804025373</v>
+        <v>2521.148040253726</v>
       </c>
       <c r="I55" t="n">
         <v>2521.148040253726</v>
@@ -63736,7 +63730,7 @@
         <v>4950</v>
       </c>
       <c r="H56" t="n">
-        <v>2471.14804025373</v>
+        <v>2471.148040253726</v>
       </c>
       <c r="I56" t="n">
         <v>2471.148040253726</v>
@@ -63777,7 +63771,7 @@
         <v>5200</v>
       </c>
       <c r="H57" t="n">
-        <v>2721.14804025373</v>
+        <v>2721.148040253726</v>
       </c>
       <c r="I57" t="n">
         <v>2721.148040253726</v>
@@ -63818,7 +63812,7 @@
         <v>5000</v>
       </c>
       <c r="H58" t="n">
-        <v>2521.14804025373</v>
+        <v>2521.148040253726</v>
       </c>
       <c r="I58" t="n">
         <v>2521.148040253726</v>
@@ -63859,7 +63853,7 @@
         <v>4950</v>
       </c>
       <c r="H59" t="n">
-        <v>2471.14804025373</v>
+        <v>2471.148040253726</v>
       </c>
       <c r="I59" t="n">
         <v>2471.148040253726</v>
@@ -63900,7 +63894,7 @@
         <v>5200</v>
       </c>
       <c r="H60" t="n">
-        <v>2721.14804025373</v>
+        <v>2721.148040253726</v>
       </c>
       <c r="I60" t="n">
         <v>2721.148040253726</v>
@@ -63941,7 +63935,7 @@
         <v>5000</v>
       </c>
       <c r="H61" t="n">
-        <v>2521.14804025373</v>
+        <v>2521.148040253726</v>
       </c>
       <c r="I61" t="n">
         <v>2521.148040253726</v>
@@ -63982,7 +63976,7 @@
         <v>4950</v>
       </c>
       <c r="H62" t="n">
-        <v>2471.14804025373</v>
+        <v>2471.148040253726</v>
       </c>
       <c r="I62" t="n">
         <v>2471.148040253726</v>
@@ -64023,7 +64017,7 @@
         <v>5200</v>
       </c>
       <c r="H63" t="n">
-        <v>2721.14804025373</v>
+        <v>2721.148040253726</v>
       </c>
       <c r="I63" t="n">
         <v>2721.148040253726</v>
@@ -64064,7 +64058,7 @@
         <v>5000</v>
       </c>
       <c r="H64" t="n">
-        <v>2521.14804025373</v>
+        <v>2521.148040253726</v>
       </c>
       <c r="I64" t="n">
         <v>2521.148040253726</v>
@@ -64105,7 +64099,7 @@
         <v>4950</v>
       </c>
       <c r="H65" t="n">
-        <v>2471.14804025373</v>
+        <v>2471.148040253726</v>
       </c>
       <c r="I65" t="n">
         <v>2471.148040253726</v>
@@ -64146,7 +64140,7 @@
         <v>4300</v>
       </c>
       <c r="H66" t="n">
-        <v>3973.06313940618</v>
+        <v>3973.063139406184</v>
       </c>
       <c r="I66" t="n">
         <v>3973.063139406184</v>
@@ -64187,7 +64181,7 @@
         <v>4000</v>
       </c>
       <c r="H67" t="n">
-        <v>3707.38106040156</v>
+        <v>3707.381060401565</v>
       </c>
       <c r="I67" t="n">
         <v>3707.381060401565</v>
@@ -64228,7 +64222,7 @@
         <v>3900</v>
       </c>
       <c r="H68" t="n">
-        <v>3607.38106040156</v>
+        <v>3607.381060401565</v>
       </c>
       <c r="I68" t="n">
         <v>3607.381060401565</v>
@@ -64269,7 +64263,7 @@
         <v>4300</v>
       </c>
       <c r="H69" t="n">
-        <v>3973.06313940618</v>
+        <v>3973.063139406184</v>
       </c>
       <c r="I69" t="n">
         <v>3973.063139406184</v>
@@ -64310,7 +64304,7 @@
         <v>4000</v>
       </c>
       <c r="H70" t="n">
-        <v>3707.38106040156</v>
+        <v>3707.381060401565</v>
       </c>
       <c r="I70" t="n">
         <v>3707.381060401565</v>
@@ -64351,7 +64345,7 @@
         <v>3900</v>
       </c>
       <c r="H71" t="n">
-        <v>3607.38106040156</v>
+        <v>3607.381060401565</v>
       </c>
       <c r="I71" t="n">
         <v>3607.381060401565</v>
@@ -64392,7 +64386,7 @@
         <v>4300</v>
       </c>
       <c r="H72" t="n">
-        <v>3973.06313940618</v>
+        <v>3973.063139406184</v>
       </c>
       <c r="I72" t="n">
         <v>3973.063139406184</v>
@@ -64433,7 +64427,7 @@
         <v>4000</v>
       </c>
       <c r="H73" t="n">
-        <v>3707.38106040156</v>
+        <v>3707.381060401565</v>
       </c>
       <c r="I73" t="n">
         <v>3707.381060401565</v>
@@ -64474,7 +64468,7 @@
         <v>3900</v>
       </c>
       <c r="H74" t="n">
-        <v>3607.38106040156</v>
+        <v>3607.381060401565</v>
       </c>
       <c r="I74" t="n">
         <v>3607.381060401565</v>
@@ -64515,7 +64509,7 @@
         <v>4300</v>
       </c>
       <c r="H75" t="n">
-        <v>3973.06313940618</v>
+        <v>3973.063139406184</v>
       </c>
       <c r="I75" t="n">
         <v>3973.063139406184</v>
@@ -64556,7 +64550,7 @@
         <v>4000</v>
       </c>
       <c r="H76" t="n">
-        <v>3707.38106040156</v>
+        <v>3707.381060401565</v>
       </c>
       <c r="I76" t="n">
         <v>3707.381060401565</v>
@@ -64597,7 +64591,7 @@
         <v>3900</v>
       </c>
       <c r="H77" t="n">
-        <v>3607.38106040156</v>
+        <v>3607.381060401565</v>
       </c>
       <c r="I77" t="n">
         <v>3607.381060401565</v>
@@ -64662,7 +64656,7 @@
         <v/>
       </c>
       <c r="G2" t="n">
-        <v>1.694065894508601e-21</v>
+        <v/>
       </c>
     </row>
     <row r="3">
